--- a/marketer_forms/007_responsive_wordpress_sidebar_contact_form--marketer_forms.xlsx
+++ b/marketer_forms/007_responsive_wordpress_sidebar_contact_form--marketer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_data</t>
+          <t>field_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>prophets</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_data</t>
+          <t>field_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>What is your email?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_data</t>
+          <t>field_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>What is your phone number?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_data</t>
+          <t>field_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>What date were you born?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_data</t>
+          <t>field_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>What time do you wake up?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_data</t>
+          <t>field_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>What is your favorite color?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_data</t>
+          <t>field_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Are you available for an appointment?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_data</t>
+          <t>field_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>What is your preferred contact method?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_data</t>
+          <t>field_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>What is the best time for you to meet?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_data</t>
+          <t>field_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>What is your preferred time zone?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,67 +745,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_data</t>
+          <t>field_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>What is the best day for you to meet?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>form_data</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>form_data</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -822,12 +776,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -850,68 +804,544 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_data_choices</t>
+          <t>field_6_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_data_choices</t>
+          <t>field_6_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_data_choices</t>
+          <t>field_6_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_data_choices</t>
+          <t>field_6_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>field_6_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>purple</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Purple</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>field_8_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>field_8_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>field_8_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>field_8_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>mail</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>field_9_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>8-12am</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>8-12am</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>field_9_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1-2pm</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1-2pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>field_9_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3-4pm</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3-4pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>field_9_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5-6pm</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>5-6pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>field_9_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7-8pm</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>7-8pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>field_9_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>9-10pm</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>9-10pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>field_9_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11pm-12am</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>11pm-12am</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>field_9_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6-7am</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>6-7am</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>field_9_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>7-8am</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>7-8am</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>field_9_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>9-10am</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>9-10am</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>field_9_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>11am-12pm</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>11am-12pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>field_10_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>utc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>field_10_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>field_10_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>cst</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>field_10_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>pst</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PST</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>field_10_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>mst</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MST</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>field_11_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>monday</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>field_11_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>tuesday</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>field_11_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>wednesday</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>field_11_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>thursday</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>field_11_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>friday</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>field_11_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>saturday</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>field_11_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>sunday</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
